--- a/global/shipping_details.xlsx
+++ b/global/shipping_details.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="62">
   <si>
     <t>port</t>
   </si>
@@ -193,6 +193,15 @@
   </si>
   <si>
     <t>Georgetown, Guyana</t>
+  </si>
+  <si>
+    <t>San Juan, Puerto Rico</t>
+  </si>
+  <si>
+    <t>PRSJU</t>
+  </si>
+  <si>
+    <t>PUERTO RICO</t>
   </si>
 </sst>
 </file>
@@ -539,7 +548,8 @@
   <cols>
     <col min="1" max="1" width="6.88671875" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="19.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.88671875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="19.6640625" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="5.33203125" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="26.33203125" style="2" bestFit="1" customWidth="1"/>
   </cols>
@@ -648,7 +658,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19" style="2" bestFit="1" customWidth="1"/>
@@ -877,6 +887,26 @@
       </c>
       <c r="F11" s="1" t="s">
         <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
